--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T07:37:23+00:00</t>
+    <t>2024-10-25T08:22:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T08:22:33+00:00</t>
+    <t>2024-10-28T11:11:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T11:11:19+00:00</t>
+    <t>2024-10-28T11:26:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T11:26:59+00:00</t>
+    <t>2024-10-29T09:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T09:20:35+00:00</t>
+    <t>2024-10-31T11:17:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T11:17:53+00:00</t>
+    <t>2024-10-31T15:29:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T15:29:56+00:00</t>
+    <t>2024-11-05T14:48:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T14:48:02+00:00</t>
+    <t>2024-11-07T21:06:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T21:06:19+00:00</t>
+    <t>2024-11-07T21:57:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T21:57:27+00:00</t>
+    <t>2024-11-07T22:09:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-09T09:07:40+00:00</t>
+    <t>2024-11-11T13:10:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:26:20+00:00</t>
+    <t>2024-11-12T06:42:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:42:28+00:00</t>
+    <t>2024-11-12T07:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T07:20:07+00:00</t>
+    <t>2024-11-12T07:35:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T07:35:41+00:00</t>
+    <t>2024-11-12T07:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T07:42:03+00:00</t>
+    <t>2024-11-12T08:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:38:00+00:00</t>
+    <t>2024-11-12T08:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:47:06+00:00</t>
+    <t>2024-11-12T20:06:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1133,9 +1133,6 @@
     <t>Claim.encounter</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Reference(Encounter)
 </t>
   </si>
@@ -1152,13 +1149,17 @@
     <t>Used in some jurisdictions to link clinical events to claim items.</t>
   </si>
   <si>
-    <t>Claim.encounter:MopedEncounter</t>
-  </si>
-  <si>
-    <t>MopedEncounter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MOPEDEncounter)
+    <t xml:space="preserve">profile:resolve()}
+</t>
+  </si>
+  <si>
+    <t>Claim.encounter:MopedEncounterKH</t>
+  </si>
+  <si>
+    <t>MopedEncounterKH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MOPEDEncounterKH)
 </t>
   </si>
   <si>
@@ -8076,7 +8077,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>358</v>
+        <v>87</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>77</v>
@@ -8091,19 +8092,19 @@
         <v>19</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>19</v>
@@ -8140,7 +8141,7 @@
         <v>19</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>19</v>
+        <v>363</v>
       </c>
       <c r="AC48" s="2"/>
       <c r="AD48" t="s" s="2">
@@ -8210,13 +8211,13 @@
         <v>367</v>
       </c>
       <c r="M49" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>19</v>
@@ -8304,7 +8305,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>77</v>
@@ -8325,13 +8326,13 @@
         <v>371</v>
       </c>
       <c r="M50" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>19</v>
@@ -19106,19 +19107,19 @@
         <v>19</v>
       </c>
       <c r="K147" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L147" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L147" t="s" s="2">
+      <c r="M147" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="M147" t="s" s="2">
+      <c r="N147" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="N147" t="s" s="2">
+      <c r="O147" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>19</v>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T20:06:39+00:00</t>
+    <t>2024-11-14T06:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T06:51:52+00:00</t>
+    <t>2024-11-14T14:31:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:31:22+00:00</t>
+    <t>2024-11-14T14:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:34:15+00:00</t>
+    <t>2024-11-14T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:43:46+00:00</t>
+    <t>2024-11-15T18:55:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1213,7 +1213,7 @@
     <t>Required to relate the current diagnosis to a package billing code that is then referenced on the individual claim items which are specific to the health condition covered by the package code.</t>
   </si>
   <si>
-    <t>http://tbd.at/MOPED-LKFAbrechnungsGruppe</t>
+    <t>http://example.org/ValueSet/moped-LKFAbrechnungsGruppe-valueset</t>
   </si>
   <si>
     <t>Claim.event</t>
@@ -2800,7 +2800,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="124.6484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.1640625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.26953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T18:55:56+00:00</t>
+    <t>2024-11-15T19:04:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T19:04:50+00:00</t>
+    <t>2024-11-15T19:21:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T19:21:45+00:00</t>
+    <t>2024-11-15T20:14:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T20:14:47+00:00</t>
+    <t>2024-11-17T19:44:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T19:44:33+00:00</t>
+    <t>2024-11-19T10:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-19T10:30:26+00:00</t>
+    <t>2025-02-10T09:28:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
